--- a/data/trans_dic/P16A11-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,87; 27,88</t>
+          <t>22,96; 28,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,77; 38,21</t>
+          <t>31,72; 37,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,36; 33,69</t>
+          <t>27,69; 33,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,06; 40,51</t>
+          <t>32,91; 40,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,93; 36,25</t>
+          <t>30,96; 35,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,89; 45,08</t>
+          <t>39,72; 45,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,43; 41,97</t>
+          <t>35,23; 41,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,11; 52,81</t>
+          <t>47,03; 52,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 31,77</t>
+          <t>28,04; 31,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,03; 41,55</t>
+          <t>37,25; 41,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,82; 37,44</t>
+          <t>32,73; 37,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,26; 47,07</t>
+          <t>42,2; 46,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,69</t>
+          <t>5,28; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 10,8</t>
+          <t>8,14; 10,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 11,96</t>
+          <t>9,24; 12,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 16,01</t>
+          <t>9,93; 16,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,22</t>
+          <t>4,86; 7,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 9,73</t>
+          <t>6,98; 9,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 12,25</t>
+          <t>9,25; 12,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 43,51</t>
+          <t>12,08; 42,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,08</t>
+          <t>5,43; 7,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,88; 9,8</t>
+          <t>7,94; 9,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,76</t>
+          <t>9,6; 11,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 31,54</t>
+          <t>12,72; 29,22</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,62</t>
+          <t>5,61; 10,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 12,89</t>
+          <t>6,94; 12,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,31</t>
+          <t>6,95; 12,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 19,94</t>
+          <t>14,13; 19,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,3</t>
+          <t>3,89; 8,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 9,6</t>
+          <t>4,33; 9,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,04</t>
+          <t>3,48; 7,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 12,05</t>
+          <t>8,5; 12,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,8</t>
+          <t>5,35; 8,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,15</t>
+          <t>6,31; 10,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,31</t>
+          <t>5,83; 9,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,82; 15,03</t>
+          <t>11,8; 15,04</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 13,9</t>
+          <t>11,58; 13,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,31; 18,07</t>
+          <t>15,33; 18,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,73; 16,17</t>
+          <t>13,77; 16,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 19,69</t>
+          <t>13,61; 19,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 18,08</t>
+          <t>15,54; 18,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,6; 22,44</t>
+          <t>19,64; 22,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 19,15</t>
+          <t>16,51; 19,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 37,19</t>
+          <t>19,74; 38,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 15,6</t>
+          <t>13,86; 15,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 19,75</t>
+          <t>17,9; 19,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 17,28</t>
+          <t>15,41; 17,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 29,18</t>
+          <t>18,56; 29,58</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>235941; 287674</t>
+          <t>236837; 290662</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>309619; 372422</t>
+          <t>309200; 369332</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206402; 254124</t>
+          <t>208891; 255953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169895; 208187</t>
+          <t>169128; 207006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>406720; 476771</t>
+          <t>407120; 473367</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>532306; 601593</t>
+          <t>530048; 608766</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>352382; 417485</t>
+          <t>350389; 415752</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>354314; 397131</t>
+          <t>353728; 396821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>660217; 745489</t>
+          <t>658047; 750417</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>855015; 959426</t>
+          <t>860139; 955334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>573973; 654766</t>
+          <t>572389; 655657</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>534973; 595940</t>
+          <t>534272; 594510</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90612; 130102</t>
+          <t>89297; 129839</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>157892; 211609</t>
+          <t>159541; 211915</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>194936; 248421</t>
+          <t>191947; 250162</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224060; 366470</t>
+          <t>227422; 366552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75951; 114562</t>
+          <t>77207; 114366</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121917; 170269</t>
+          <t>122226; 170963</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>184277; 243650</t>
+          <t>183819; 243971</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>271119; 973320</t>
+          <t>270184; 949187</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>175595; 232112</t>
+          <t>178130; 230013</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>292516; 363611</t>
+          <t>294638; 363648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>392663; 477935</t>
+          <t>390290; 471617</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>569675; 1427522</t>
+          <t>575578; 1322862</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31090; 58556</t>
+          <t>30941; 57399</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32775; 61906</t>
+          <t>33327; 61810</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39075; 67309</t>
+          <t>38022; 66008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92259; 128964</t>
+          <t>91355; 127506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18883; 39550</t>
+          <t>18547; 39249</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18763; 43923</t>
+          <t>19819; 44106</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19010; 44162</t>
+          <t>19099; 42626</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56300; 79584</t>
+          <t>56113; 79856</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55824; 90480</t>
+          <t>54944; 89318</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59572; 95208</t>
+          <t>59156; 98669</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63986; 102079</t>
+          <t>63944; 101243</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>154494; 196446</t>
+          <t>154252; 196529</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>379776; 455223</t>
+          <t>379184; 449429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>522824; 617190</t>
+          <t>523474; 616607</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>463584; 546225</t>
+          <t>465145; 548358</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>477531; 679271</t>
+          <t>469665; 674367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>520780; 611006</t>
+          <t>525033; 608714</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>694437; 795031</t>
+          <t>695863; 792747</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>578283; 676429</t>
+          <t>583162; 677769</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>719005; 1357333</t>
+          <t>720288; 1420887</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>920899; 1037997</t>
+          <t>922669; 1040186</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1243256; 1374023</t>
+          <t>1245616; 1375353</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1069920; 1193793</t>
+          <t>1064886; 1195175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1314130; 2071342</t>
+          <t>1317410; 2100399</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A11-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,96; 28,17</t>
+          <t>23,0; 28,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,72; 37,89</t>
+          <t>31,49; 37,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,69; 33,93</t>
+          <t>27,43; 33,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,91; 40,28</t>
+          <t>31,4; 38,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,96; 35,99</t>
+          <t>30,88; 36,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,72; 45,62</t>
+          <t>39,86; 45,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,23; 41,8</t>
+          <t>35,44; 41,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,03; 52,76</t>
+          <t>46,15; 51,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,04; 31,98</t>
+          <t>28,23; 31,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,25; 41,37</t>
+          <t>36,93; 41,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,73; 37,49</t>
+          <t>32,91; 37,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,2; 46,96</t>
+          <t>40,92; 45,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,67</t>
+          <t>5,37; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 10,81</t>
+          <t>8,06; 10,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,05</t>
+          <t>9,32; 12,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 16,01</t>
+          <t>13,85; 16,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,2</t>
+          <t>4,86; 7,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 9,77</t>
+          <t>6,89; 9,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 12,27</t>
+          <t>9,28; 12,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 42,43</t>
+          <t>11,99; 14,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,01</t>
+          <t>5,41; 7,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 9,8</t>
+          <t>7,92; 9,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 11,6</t>
+          <t>9,51; 11,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,72; 29,22</t>
+          <t>13,3; 15,19</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,41</t>
+          <t>5,67; 10,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,87</t>
+          <t>6,86; 12,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 12,07</t>
+          <t>7,05; 12,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 19,72</t>
+          <t>14,42; 19,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,24</t>
+          <t>4,1; 8,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,64</t>
+          <t>4,0; 9,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,76</t>
+          <t>3,4; 8,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,09</t>
+          <t>9,0; 12,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,69</t>
+          <t>5,43; 8,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,52</t>
+          <t>6,28; 10,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,24</t>
+          <t>5,81; 9,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 15,04</t>
+          <t>12,19; 15,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 13,72</t>
+          <t>11,61; 13,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 18,06</t>
+          <t>15,44; 18,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 16,24</t>
+          <t>13,66; 16,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,61; 19,55</t>
+          <t>17,69; 20,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,54; 18,01</t>
+          <t>15,53; 18,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,64; 22,38</t>
+          <t>19,57; 22,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 19,19</t>
+          <t>16,44; 19,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,74; 38,93</t>
+          <t>19,47; 21,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 15,63</t>
+          <t>13,76; 15,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 19,77</t>
+          <t>17,96; 19,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 17,3</t>
+          <t>15,34; 17,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 29,58</t>
+          <t>18,85; 20,49</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>188107</t>
+          <t>203339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>375088</t>
+          <t>400631</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>563194</t>
+          <t>603970</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>236837; 290662</t>
+          <t>237290; 291134</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>309200; 369332</t>
+          <t>306889; 368749</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>208891; 255953</t>
+          <t>206935; 256024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169128; 207006</t>
+          <t>181374; 224650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>407120; 473367</t>
+          <t>406156; 475747</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>530048; 608766</t>
+          <t>531954; 603894</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>350389; 415752</t>
+          <t>352551; 417702</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>353728; 396821</t>
+          <t>378448; 422400</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>658047; 750417</t>
+          <t>662418; 748764</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>860139; 955334</t>
+          <t>852712; 951556</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>572389; 655657</t>
+          <t>575671; 654659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>534272; 594510</t>
+          <t>571944; 634186</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314896</t>
+          <t>337529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>460172</t>
+          <t>286480</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>775067</t>
+          <t>624009</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89297; 129839</t>
+          <t>90925; 131093</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>159541; 211915</t>
+          <t>158028; 212138</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>191947; 250162</t>
+          <t>193543; 249788</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>227422; 366552</t>
+          <t>308883; 371084</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77207; 114366</t>
+          <t>77109; 117000</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122226; 170963</t>
+          <t>120668; 169196</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>183819; 243971</t>
+          <t>184562; 244749</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>270184; 949187</t>
+          <t>260287; 311093</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178130; 230013</t>
+          <t>177406; 230850</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>294638; 363648</t>
+          <t>294071; 366798</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>390290; 471617</t>
+          <t>386371; 473241</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>575578; 1322862</t>
+          <t>585300; 668383</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108967</t>
+          <t>120157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66792</t>
+          <t>78443</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>175758</t>
+          <t>198600</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30941; 57399</t>
+          <t>31251; 58766</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33327; 61810</t>
+          <t>32971; 61299</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38022; 66008</t>
+          <t>38578; 67330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91355; 127506</t>
+          <t>102622; 139822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18547; 39249</t>
+          <t>19520; 40532</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19819; 44106</t>
+          <t>18308; 42877</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19099; 42626</t>
+          <t>18673; 44125</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56113; 79856</t>
+          <t>66172; 92195</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54944; 89318</t>
+          <t>55772; 88764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59156; 98669</t>
+          <t>58925; 97201</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63944; 101243</t>
+          <t>63638; 102143</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>154252; 196529</t>
+          <t>176270; 221473</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611969</t>
+          <t>661025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>902051</t>
+          <t>765554</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1514020</t>
+          <t>1426579</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>379184; 449429</t>
+          <t>380247; 452546</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>523474; 616607</t>
+          <t>527370; 616299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>465145; 548358</t>
+          <t>461433; 544056</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>469665; 674367</t>
+          <t>622391; 706139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>525033; 608714</t>
+          <t>524789; 611644</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>695863; 792747</t>
+          <t>693181; 792455</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>583162; 677769</t>
+          <t>580645; 676884</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>720288; 1420887</t>
+          <t>725561; 804393</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>922669; 1040186</t>
+          <t>915783; 1028937</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1245616; 1375353</t>
+          <t>1249757; 1376411</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1064886; 1195175</t>
+          <t>1060195; 1188443</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1317410; 2100399</t>
+          <t>1365839; 1484748</t>
         </is>
       </c>
     </row>
